--- a/data/trans_bre/P1410-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P1410-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,23</t>
+          <t>-0,03</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-21,5%</t>
+          <t>-3,85%</t>
         </is>
       </c>
     </row>
@@ -665,17 +665,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 2,29</t>
+          <t>-0,36; 2,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 1,42</t>
+          <t>-0,74; 1,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 1,73</t>
+          <t>-2,65; 1,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-79,96; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,03</t>
+          <t>0,02</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,8</t>
+          <t>-0,48; 0,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 0,64</t>
+          <t>-0,6; 0,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,56</t>
+          <t>0,17; 1,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 1,1</t>
+          <t>-1,0; 0,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,41</t>
+          <t>-0,16</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-37,16%</t>
+          <t>-16,7%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,06</t>
+          <t>0,19; 2,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,68</t>
+          <t>-0,89; 1,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,01; 1,81</t>
+          <t>0,02; 1,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 0,49</t>
+          <t>-1,3; 0,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,3; —</t>
+          <t>-29,24; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-54,47; 357,62</t>
+          <t>-62,57; 302,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-49,53; —</t>
+          <t>-36,66; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-86,95; 138,59</t>
+          <t>-77,7; 264,3</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,28</t>
+          <t>-0,91</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-12,09%</t>
+          <t>-28,87%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 1,32</t>
+          <t>-2,95; 1,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 0,13</t>
+          <t>-2,85; 0,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 2,19</t>
+          <t>-1,19; 2,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 1,63</t>
+          <t>-2,56; 0,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-69,46; 76,37</t>
+          <t>-66,35; 68,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-91,32; 33,46</t>
+          <t>-89,71; 57,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-40,27; 198,34</t>
+          <t>-48,03; 175,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-53,29; 134,62</t>
+          <t>-60,23; 27,38</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-5,45</t>
+          <t>-5,34</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-62,86%</t>
+          <t>-61,86%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,8; -2,38</t>
+          <t>-9,69; -2,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 3,58</t>
+          <t>-2,36; 3,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 0,52</t>
+          <t>-5,6; 0,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,13; -3,0</t>
+          <t>-7,95; -2,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-74,34; -23,76</t>
+          <t>-73,45; -23,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-38,25; 95,34</t>
+          <t>-36,41; 93,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-68,89; 13,24</t>
+          <t>-70,84; 7,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-76,48; -40,32</t>
+          <t>-76,08; -41,14</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-5,46</t>
+          <t>-2,69</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-56,03%</t>
+          <t>-28,8%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,59; -0,54</t>
+          <t>-10,97; -0,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 2,61</t>
+          <t>-6,36; 3,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 4,52</t>
+          <t>-5,9; 4,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,81; -2,13</t>
+          <t>-5,94; 0,2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-60,55; -1,01</t>
+          <t>-60,95; -6,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-48,57; 37,53</t>
+          <t>-51,64; 39,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-37,17; 45,63</t>
+          <t>-37,99; 44,07</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-83,99; -24,85</t>
+          <t>-52,19; 2,31</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-2,2</t>
+          <t>-2,74</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-10,48%</t>
+          <t>-12,82%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,88; 0,44</t>
+          <t>-13,0; 0,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,32; 3,26</t>
+          <t>-9,89; 3,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 6,98</t>
+          <t>-4,52; 7,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 2,33</t>
+          <t>-7,62; 1,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-49,78; 3,47</t>
+          <t>-49,85; 4,05</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-38,71; 19,29</t>
+          <t>-38,03; 22,46</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-25,5; 55,71</t>
+          <t>-23,89; 55,0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-28,27; 12,93</t>
+          <t>-31,42; 9,43</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-1,08</t>
+          <t>-1,04</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-21,13%</t>
+          <t>-19,21%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 0,25</t>
+          <t>-1,77; 0,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 1,26</t>
+          <t>-0,7; 1,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 1,85</t>
+          <t>-0,26; 1,74</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 0,28</t>
+          <t>-2,02; -0,19</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-36,45; 6,14</t>
+          <t>-35,35; 3,7</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-14,79; 39,18</t>
+          <t>-16,87; 36,96</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 55,83</t>
+          <t>-6,03; 53,74</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-36,57; 4,99</t>
+          <t>-33,81; -3,76</t>
         </is>
       </c>
     </row>
